--- a/src/prommis/solvent_extraction/data for parmest.xlsx
+++ b/src/prommis/solvent_extraction/data for parmest.xlsx
@@ -1,30 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ad00105\Desktop\Model_software\prommis\src\prommis\solvent_extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F811EED-0D76-4033-B95E-9CD4BF3AB475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D820306-4312-4B73-B1B7-10239D8CC8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="1785" windowWidth="25440" windowHeight="15270" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="1785" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="model validation new" sheetId="4" r:id="rId4"/>
-    <sheet name="model validation" sheetId="5" r:id="rId5"/>
-    <sheet name="parameter values" sheetId="6" r:id="rId6"/>
-    <sheet name="parameter values feed dosage" sheetId="7" r:id="rId7"/>
-    <sheet name="parameter values out dosage" sheetId="8" r:id="rId8"/>
-    <sheet name="impurities new" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet2 (2)" sheetId="14" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="model validation new" sheetId="4" r:id="rId5"/>
+    <sheet name="model validation" sheetId="5" r:id="rId6"/>
+    <sheet name="parameter values" sheetId="6" r:id="rId7"/>
+    <sheet name="parameter values feed dosage" sheetId="7" r:id="rId8"/>
+    <sheet name="parameter values out dosage" sheetId="8" r:id="rId9"/>
     <sheet name="impurities" sheetId="10" r:id="rId10"/>
-    <sheet name="new parameter values" sheetId="11" r:id="rId11"/>
-    <sheet name="Fe only" sheetId="12" r:id="rId12"/>
+    <sheet name="impurities new" sheetId="9" r:id="rId11"/>
+    <sheet name="new parameter values" sheetId="11" r:id="rId12"/>
+    <sheet name="Fe only" sheetId="12" r:id="rId13"/>
+    <sheet name="Fe only (2)" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="65">
   <si>
     <t>dosage</t>
   </si>
@@ -213,6 +215,33 @@
   <si>
     <t>w</t>
   </si>
+  <si>
+    <t>E Y</t>
+  </si>
+  <si>
+    <t>E Ce</t>
+  </si>
+  <si>
+    <t>E Nd</t>
+  </si>
+  <si>
+    <t>E Sm</t>
+  </si>
+  <si>
+    <t>E Gd</t>
+  </si>
+  <si>
+    <t>E Dy</t>
+  </si>
+  <si>
+    <t>E La</t>
+  </si>
+  <si>
+    <t>E Pr</t>
+  </si>
+  <si>
+    <t>A/O</t>
+  </si>
 </sst>
 </file>
 
@@ -251,7 +280,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,6 +290,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -354,6 +401,11 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,11 +685,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16AAF83-F84A-48AC-90E6-43D075812AD2}">
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -663,70 +715,142 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
         <v>4.9878531370748496</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>0.24099999999999999</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="7">
         <v>-1.64</v>
       </c>
       <c r="D2">
-        <v>-1.92</v>
-      </c>
-      <c r="E2">
+        <v>-1.36</v>
+      </c>
+      <c r="E2" s="7">
         <v>-1.81</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>-1.67</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="7">
         <v>-1.85</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="7">
         <v>-1.74</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>-1.36</v>
+      </c>
+      <c r="K2" s="7">
+        <v>1</v>
+      </c>
+      <c r="L2" s="7">
+        <v>5</v>
+      </c>
+      <c r="M2" s="7">
+        <v>5</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7">
+        <v>1</v>
+      </c>
+      <c r="P2" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+      <c r="S2" s="7">
+        <v>2.2395622457170412</v>
+      </c>
+      <c r="T2" s="7">
+        <v>4.1825819962989419</v>
+      </c>
+      <c r="U2" s="7">
+        <v>2.0932100521339581</v>
+      </c>
+      <c r="V2" s="7">
+        <v>1.3928628341453531</v>
+      </c>
+      <c r="W2" s="7">
+        <v>1.7871795372261761</v>
+      </c>
+      <c r="X2" s="7">
+        <v>1.4909941389328649</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>1.1879817525171541</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>1.5251941583177719</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>4.9785421780668777</v>
       </c>
       <c r="B3">
@@ -751,26 +875,62 @@
         <v>-1.47</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>-1.53</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
+        <v>5</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>6.6114061337195604</v>
+      </c>
+      <c r="T3">
+        <v>3.205177802787111</v>
+      </c>
+      <c r="U3">
+        <v>2.803186715169653</v>
+      </c>
+      <c r="V3">
+        <v>2.3426369721582359</v>
+      </c>
+      <c r="W3">
+        <v>2.5059821239382138</v>
+      </c>
+      <c r="X3">
+        <v>3.2773891454587498</v>
+      </c>
+      <c r="Y3">
+        <v>2.866609580241787</v>
+      </c>
+      <c r="Z3">
+        <v>5.9350943102767584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>4.9294758200052957</v>
       </c>
       <c r="B4">
@@ -795,70 +955,142 @@
         <v>-0.98</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>-1.53</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>-1.46</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>5</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>25.746444105693019</v>
+      </c>
+      <c r="T4">
+        <v>2.9976589159516012</v>
+      </c>
+      <c r="U4">
+        <v>3.351171054837125</v>
+      </c>
+      <c r="V4">
+        <v>2.7411274627306499</v>
+      </c>
+      <c r="W4">
+        <v>3.6626441176046929</v>
+      </c>
+      <c r="X4">
+        <v>9.4787395973196098</v>
+      </c>
+      <c r="Y4">
+        <v>2.866609580241787</v>
+      </c>
+      <c r="Z4">
+        <v>3.3511710548371201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
         <v>4.8132193011041764</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="10">
         <v>1.137</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="10">
         <v>0.35</v>
       </c>
       <c r="D5">
         <v>-1.34</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="10">
         <v>-1.44</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="10">
         <v>-1.55</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="10">
         <v>-1.1599999999999999</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="10">
         <v>-0.24</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="I5" s="10">
+        <v>-1.53</v>
+      </c>
+      <c r="J5" s="10">
+        <v>-1.44</v>
+      </c>
+      <c r="K5" s="10">
+        <v>1</v>
+      </c>
+      <c r="L5" s="7">
+        <v>5</v>
+      </c>
+      <c r="M5" s="7">
+        <v>5</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>1</v>
+      </c>
+      <c r="S5" s="10">
+        <v>69.123615241476301</v>
+      </c>
+      <c r="T5" s="10">
+        <v>4.3710847735683966</v>
+      </c>
+      <c r="U5" s="10">
+        <v>3.5035734831986272</v>
+      </c>
+      <c r="V5" s="10">
+        <v>2.7411274627306499</v>
+      </c>
+      <c r="W5" s="10">
+        <v>6.4706500953921759</v>
+      </c>
+      <c r="X5" s="10">
+        <v>36.525666494768323</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>2.866609580241787</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>6.7550028996576179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>4.751685080492198</v>
       </c>
       <c r="B6">
@@ -883,26 +1115,62 @@
         <v>0.26</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>-1.22</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>-1.32</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
+      <c r="L6" s="7">
+        <v>5</v>
+      </c>
+      <c r="M6" s="7">
+        <v>5</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>88.113778355369817</v>
+      </c>
+      <c r="T6">
+        <v>4.7726721034203887</v>
+      </c>
+      <c r="U6">
+        <v>4.5676781039662373</v>
+      </c>
+      <c r="V6">
+        <v>7.2033158503842589</v>
+      </c>
+      <c r="W6">
+        <v>13.680688860321</v>
+      </c>
+      <c r="X6">
+        <v>64.535245043938247</v>
+      </c>
+      <c r="Y6">
+        <v>5.6831520840097216</v>
+      </c>
+      <c r="Z6">
+        <v>4.1825819962989419</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>4.7231095025915941</v>
       </c>
       <c r="B7">
@@ -927,26 +1195,62 @@
         <v>0.61</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>-1.22</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>-1.19</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
+      <c r="L7" s="7">
+        <v>5</v>
+      </c>
+      <c r="M7" s="7">
+        <v>5</v>
       </c>
       <c r="N7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>94.064905689723247</v>
+      </c>
+      <c r="T7">
+        <v>6.3326875310947912</v>
+      </c>
+      <c r="U7">
+        <v>6.0649558509397794</v>
+      </c>
+      <c r="V7">
+        <v>12.377068106893541</v>
+      </c>
+      <c r="W7">
+        <v>23.194799683241602</v>
+      </c>
+      <c r="X7">
+        <v>80.290917015381595</v>
+      </c>
+      <c r="Y7">
+        <v>5.6831520840097216</v>
+      </c>
+      <c r="Z7">
+        <v>10.08826283567233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>4.7094378121328804</v>
       </c>
       <c r="B8">
@@ -971,70 +1275,142 @@
         <v>0.77</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L8" s="7">
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>95.724158885346398</v>
+      </c>
+      <c r="T8">
+        <v>8.7174188254586831</v>
+      </c>
+      <c r="U8">
+        <v>9.0909090909090917</v>
+      </c>
+      <c r="V8">
+        <v>16.00493053652465</v>
+      </c>
+      <c r="W8">
+        <v>31.369974231668749</v>
+      </c>
+      <c r="X8">
+        <v>85.482917753175954</v>
+      </c>
+      <c r="Y8">
+        <v>11.41230574141505</v>
+      </c>
+      <c r="Z8">
+        <v>11.647171194356069</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
         <v>1.9915790348048139</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>0.235616438356164</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>-1.614154798725508</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="7">
         <v>-1.852615520079504</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="7">
         <v>-1.741725335781714</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>-1.852615520079504</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="7">
         <v>-1.65282239968498</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="7">
         <v>-1.741725335781714</v>
       </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <v>5</v>
+      </c>
+      <c r="M9" s="7">
+        <v>5</v>
+      </c>
+      <c r="N9" s="7">
+        <v>1</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7">
+        <v>2.3736263736263585</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1.3846153846153493</v>
+      </c>
+      <c r="U9" s="7">
+        <v>1.7802197802197592</v>
+      </c>
+      <c r="V9" s="7">
+        <v>1.3846153846153493</v>
+      </c>
+      <c r="W9" s="7">
+        <v>2.1758241758241397</v>
+      </c>
+      <c r="X9" s="7">
+        <v>1.7802197802197592</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>1.980691304582046</v>
       </c>
       <c r="B10">
@@ -1059,26 +1435,62 @@
         <v>-1.514596939418587</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
+      <c r="L10" s="7">
+        <v>5</v>
+      </c>
+      <c r="M10" s="7">
+        <v>5</v>
       </c>
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>6.329670329670317</v>
+      </c>
+      <c r="T10">
+        <v>3.3626373626373383</v>
+      </c>
+      <c r="U10">
+        <v>2.9670329670329285</v>
+      </c>
+      <c r="V10">
+        <v>2.571428571428549</v>
+      </c>
+      <c r="W10">
+        <v>2.571428571428549</v>
+      </c>
+      <c r="X10">
+        <v>2.9670329670329285</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>1.9336677366397059</v>
       </c>
       <c r="B11">
@@ -1103,70 +1515,142 @@
         <v>-0.95957134294439284</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>5</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>25.912087912087799</v>
+      </c>
+      <c r="T11" s="11">
+        <v>3.1648351648351496</v>
+      </c>
+      <c r="U11">
+        <v>3.3626373626373383</v>
+      </c>
+      <c r="V11">
+        <v>2.7692307692307394</v>
+      </c>
+      <c r="W11">
+        <v>3.56043956043953</v>
+      </c>
+      <c r="X11">
+        <v>9.8901098901098674</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
         <v>1.827040781438199</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="10">
         <v>1.1671232876712301</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="10">
         <v>0.34014801111555087</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="10">
         <v>-1.3631242825001839</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="10">
         <v>-1.4327516043600459</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="10">
         <v>-1.578511869553177</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="10">
         <v>-1.142053948747725</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="10">
         <v>-0.24615343666192119</v>
       </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="I12" s="10">
+        <v>0</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
+        <v>1</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12" s="10">
+        <v>1</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
+        <v>0</v>
+      </c>
+      <c r="S12" s="10">
+        <v>68.637362637362614</v>
+      </c>
+      <c r="T12" s="10">
+        <v>4.1538461538461409</v>
+      </c>
+      <c r="U12" s="10">
+        <v>3.56043956043953</v>
+      </c>
+      <c r="V12" s="10">
+        <v>2.571428571428549</v>
+      </c>
+      <c r="W12" s="10">
+        <v>6.7252747252746978</v>
+      </c>
+      <c r="X12" s="10">
+        <v>36.197802197802098</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <v>1.7705451871527289</v>
       </c>
       <c r="B13">
@@ -1191,26 +1675,62 @@
         <v>0.25527250510330463</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>87.428571428571402</v>
+      </c>
+      <c r="T13">
+        <v>4.7472527472527402</v>
+      </c>
+      <c r="U13">
+        <v>4.5494505494505493</v>
+      </c>
+      <c r="V13">
+        <v>7.5164835164834978</v>
+      </c>
+      <c r="W13">
+        <v>13.846153846153793</v>
+      </c>
+      <c r="X13">
+        <v>64.285714285714207</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <v>1.7440974190635239</v>
       </c>
       <c r="B14">
@@ -1235,26 +1755,62 @@
         <v>0.59434585455452171</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>93.956043956043899</v>
+      </c>
+      <c r="T14">
+        <v>6.5274725274725096</v>
+      </c>
+      <c r="U14">
+        <v>6.1318681318681314</v>
+      </c>
+      <c r="V14">
+        <v>12.659340659340595</v>
+      </c>
+      <c r="W14">
+        <v>23.340659340659293</v>
+      </c>
+      <c r="X14">
+        <v>79.714285714285694</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>1.7322008018720709</v>
       </c>
       <c r="B15">
@@ -1279,26 +1835,62 @@
         <v>0.76199725943106256</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>95.538461538461505</v>
+      </c>
+      <c r="T15">
+        <v>9.0989010989010772</v>
+      </c>
+      <c r="U15">
+        <v>9.0989010989010772</v>
+      </c>
+      <c r="V15">
+        <v>16.219780219780201</v>
+      </c>
+      <c r="W15">
+        <v>31.450549450549399</v>
+      </c>
+      <c r="X15">
+        <v>85.252747252747199</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <v>1.7069872080419219</v>
       </c>
       <c r="B16">
@@ -1323,22 +1915,298 @@
         <v>1.206967825528747</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>98.505494505494497</v>
+      </c>
+      <c r="T16">
+        <v>10.087912087911995</v>
+      </c>
+      <c r="U16">
+        <v>10.681318681318601</v>
+      </c>
+      <c r="V16">
+        <v>30.857142857142801</v>
+      </c>
+      <c r="W16">
+        <v>55.978021978021907</v>
+      </c>
+      <c r="X16">
+        <v>94.153846153846104</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <v>25</v>
+      </c>
+      <c r="B17" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <v>-0.26750963699125352</v>
+      </c>
+      <c r="E17" s="12">
+        <v>-5.5316923634942707E-2</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>-0.20910908521850771</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
+        <v>-0.61134831389953581</v>
+      </c>
+      <c r="J17" s="12">
+        <v>-1.7026524217189538E-2</v>
+      </c>
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
+      <c r="L17" s="12">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12">
+        <v>1</v>
+      </c>
+      <c r="N17" s="12">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12">
+        <v>0</v>
+      </c>
+      <c r="P17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>1</v>
+      </c>
+      <c r="R17" s="12">
+        <v>1</v>
+      </c>
+      <c r="S17" s="12">
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <v>35.07</v>
+      </c>
+      <c r="U17" s="12">
+        <v>46.82</v>
+      </c>
+      <c r="V17" s="12">
+        <v>0</v>
+      </c>
+      <c r="W17" s="12">
+        <v>38.19</v>
+      </c>
+      <c r="X17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>19.66</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>49.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.25573196162710737</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.54236684047993289</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>-3.1804562525097141E-2</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>-0.1512553277727009</v>
+      </c>
+      <c r="J18" s="7">
+        <v>0.21796179846852079</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18" s="12">
+        <v>1</v>
+      </c>
+      <c r="M18" s="12">
+        <v>1</v>
+      </c>
+      <c r="N18" s="7">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>1</v>
+      </c>
+      <c r="R18" s="7">
+        <v>1</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0</v>
+      </c>
+      <c r="T18" s="7">
+        <v>64.31</v>
+      </c>
+      <c r="U18" s="7">
+        <v>77.709999999999994</v>
+      </c>
+      <c r="V18" s="7">
+        <v>0</v>
+      </c>
+      <c r="W18" s="7">
+        <v>48.17</v>
+      </c>
+      <c r="X18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="7">
+        <v>41.38</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>62.29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <v>2.5</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0.29563415617744288</v>
+      </c>
+      <c r="E19">
+        <v>0.54866024026583626</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>-3.076090305997338E-2</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>-9.1714900819881665E-2</v>
+      </c>
+      <c r="J19">
+        <v>0.50346445715765153</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12">
+        <v>1</v>
+      </c>
+      <c r="M19" s="12">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" s="7">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>66.39</v>
+      </c>
+      <c r="U19">
+        <v>77.959999999999994</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>48.23</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>44.74</v>
+      </c>
+      <c r="Z19">
+        <v>76.12</v>
       </c>
     </row>
   </sheetData>
@@ -1921,6 +2789,500 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>0.37890162349538931</v>
+      </c>
+      <c r="D2">
+        <v>-0.55880438484237782</v>
+      </c>
+      <c r="E2">
+        <v>-0.22018318867981981</v>
+      </c>
+      <c r="F2">
+        <v>0.28887120618536088</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>44.37</v>
+      </c>
+      <c r="L2">
+        <v>8.43</v>
+      </c>
+      <c r="M2">
+        <v>16.72</v>
+      </c>
+      <c r="N2">
+        <v>39.33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.74730347581587131</v>
+      </c>
+      <c r="D3">
+        <v>-0.25642653036117807</v>
+      </c>
+      <c r="E3">
+        <v>-9.619521531998218E-2</v>
+      </c>
+      <c r="F3">
+        <v>0.41814043679433921</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>65.069999999999993</v>
+      </c>
+      <c r="L3">
+        <v>15.59</v>
+      </c>
+      <c r="M3">
+        <v>21.08</v>
+      </c>
+      <c r="N3">
+        <v>46.61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>0.81772606167682238</v>
+      </c>
+      <c r="D4">
+        <v>-0.12006930682745021</v>
+      </c>
+      <c r="E4">
+        <v>-1.048649293295891E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.47260455139702251</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>68.66</v>
+      </c>
+      <c r="L4">
+        <v>20.18</v>
+      </c>
+      <c r="M4">
+        <v>24.55</v>
+      </c>
+      <c r="N4">
+        <v>49.74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="C5">
+        <v>0.94732133535924345</v>
+      </c>
+      <c r="D5">
+        <v>7.2103517063392866E-2</v>
+      </c>
+      <c r="E5">
+        <v>0.15970084286751191</v>
+      </c>
+      <c r="F5">
+        <v>0.52895058389195404</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>74.7</v>
+      </c>
+      <c r="L5">
+        <v>28.24</v>
+      </c>
+      <c r="M5">
+        <v>32.5</v>
+      </c>
+      <c r="N5">
+        <v>52.98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>1.00311120790082</v>
+      </c>
+      <c r="D6">
+        <v>0.27645618591098309</v>
+      </c>
+      <c r="E6">
+        <v>0.2413180682920206</v>
+      </c>
+      <c r="F6">
+        <v>0.63375355796501509</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>77.05</v>
+      </c>
+      <c r="L6">
+        <v>38.65</v>
+      </c>
+      <c r="M6">
+        <v>36.75</v>
+      </c>
+      <c r="N6">
+        <v>58.92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>0.19</v>
+      </c>
+      <c r="C7">
+        <v>0.2019624381862466</v>
+      </c>
+      <c r="D7">
+        <v>0.73398894149761618</v>
+      </c>
+      <c r="E7">
+        <v>2.2411320697578532E-2</v>
+      </c>
+      <c r="F7">
+        <v>0.37467651080669062</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>34.67</v>
+      </c>
+      <c r="L7">
+        <v>64.37</v>
+      </c>
+      <c r="M7">
+        <v>25.98</v>
+      </c>
+      <c r="N7">
+        <v>44.13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>0.76789849152443013</v>
+      </c>
+      <c r="D8">
+        <v>-0.26172914980845402</v>
+      </c>
+      <c r="E8">
+        <v>-9.0732996238242117E-2</v>
+      </c>
+      <c r="F8">
+        <v>0.41866397556212759</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>66.14</v>
+      </c>
+      <c r="L8">
+        <v>15.43</v>
+      </c>
+      <c r="M8">
+        <v>21.29</v>
+      </c>
+      <c r="N8">
+        <v>46.64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>0.99</v>
+      </c>
+      <c r="C9">
+        <v>1.224347751283891</v>
+      </c>
+      <c r="D9">
+        <v>-0.60959581881686786</v>
+      </c>
+      <c r="E9">
+        <v>-0.23437228355177231</v>
+      </c>
+      <c r="F9">
+        <v>0.46721891154789469</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>84.82</v>
+      </c>
+      <c r="L9">
+        <v>7.57</v>
+      </c>
+      <c r="M9">
+        <v>16.27</v>
+      </c>
+      <c r="N9">
+        <v>49.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1.49</v>
+      </c>
+      <c r="C10">
+        <v>1.78025349022115</v>
+      </c>
+      <c r="D10">
+        <v>-0.65230372820996729</v>
+      </c>
+      <c r="E10">
+        <v>-0.52714761933160048</v>
+      </c>
+      <c r="F10">
+        <v>0.60236401267877693</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>95.26</v>
+      </c>
+      <c r="L10">
+        <v>6.91</v>
+      </c>
+      <c r="M10">
+        <v>9.01</v>
+      </c>
+      <c r="N10">
+        <v>57.16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>1.79</v>
+      </c>
+      <c r="C11">
+        <v>1.9074053552227761</v>
+      </c>
+      <c r="D11">
+        <v>-1.574557366498176</v>
+      </c>
+      <c r="E11">
+        <v>-0.56219097385209027</v>
+      </c>
+      <c r="F11">
+        <v>0.8488269794820742</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>96.42</v>
+      </c>
+      <c r="L11">
+        <v>0.88</v>
+      </c>
+      <c r="M11">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="N11">
+        <v>70.180000000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2080,7 +3442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3408,9 +4770,1026 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED20A37-8650-4215-A096-B0336A7BDE3B}">
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1.5</v>
+      </c>
+      <c r="B2">
+        <v>0.75908372827804105</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>3.3548387096774199</v>
+      </c>
+      <c r="E2">
+        <v>3.4712950600801068E-2</v>
+      </c>
+      <c r="F2">
+        <v>-1.459508469728648</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1.5</v>
+      </c>
+      <c r="B3">
+        <v>0.922432859399684</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>3.87096774193548</v>
+      </c>
+      <c r="E3">
+        <v>4.0268456375838882E-2</v>
+      </c>
+      <c r="F3">
+        <v>-1.3950350180286311</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1.5</v>
+      </c>
+      <c r="B4">
+        <v>1.24391785150078</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>6.9677419354838497</v>
+      </c>
+      <c r="E4">
+        <v>7.4895977808598913E-2</v>
+      </c>
+      <c r="F4">
+        <v>-1.1255415048964621</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1.5</v>
+      </c>
+      <c r="B5">
+        <v>1.4541864139020499</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>17.5483870967741</v>
+      </c>
+      <c r="E5">
+        <v>0.21283255086071851</v>
+      </c>
+      <c r="F5">
+        <v>-0.67196194978818546</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5984202211690299</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>25.2903225806451</v>
+      </c>
+      <c r="E6">
+        <v>0.33851468048359129</v>
+      </c>
+      <c r="F6">
+        <v>-0.47042249237096162</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1.5</v>
+      </c>
+      <c r="B7">
+        <v>1.81216429699842</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>32.774193548387103</v>
+      </c>
+      <c r="E7">
+        <v>0.48752399232245702</v>
+      </c>
+      <c r="F7">
+        <v>-0.31200400667958628</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1.25</v>
+      </c>
+      <c r="B8">
+        <v>0.75908372827804105</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>6.9677419354838497</v>
+      </c>
+      <c r="E8">
+        <v>7.4895977808598913E-2</v>
+      </c>
+      <c r="F8">
+        <v>-1.1255415048964621</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1.25</v>
+      </c>
+      <c r="B9">
+        <v>0.89810426540284305</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="F9">
+        <v>-1.060697840353612</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1.25</v>
+      </c>
+      <c r="B10">
+        <v>1.23522906793048</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>20.387096774193498</v>
+      </c>
+      <c r="E10">
+        <v>0.25607779578606082</v>
+      </c>
+      <c r="F10">
+        <v>-0.59162807707882048</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1.25</v>
+      </c>
+      <c r="B11">
+        <v>1.3690363349131101</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>30.451612903225701</v>
+      </c>
+      <c r="E11">
+        <v>0.43784786641929291</v>
+      </c>
+      <c r="F11">
+        <v>-0.35867676221663419</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1.25</v>
+      </c>
+      <c r="B12">
+        <v>1.5897314375987299</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>39.4838709677419</v>
+      </c>
+      <c r="E12">
+        <v>0.65245202558635296</v>
+      </c>
+      <c r="F12">
+        <v>-0.18545141623350389</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1.25</v>
+      </c>
+      <c r="B13">
+        <v>1.76524486571879</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>45.677419354838698</v>
+      </c>
+      <c r="E13">
+        <v>0.84085510688836063</v>
+      </c>
+      <c r="F13">
+        <v>-7.5278833809880707E-2</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>0.75039494470774004</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>12.1290322580645</v>
+      </c>
+      <c r="E14">
+        <v>0.13803230543318629</v>
+      </c>
+      <c r="F14">
+        <v>-0.86001925831308712</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>0.89984202211690301</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>20.645161290322498</v>
+      </c>
+      <c r="E15">
+        <v>0.26016260162601501</v>
+      </c>
+      <c r="F15">
+        <v>-0.58475513311949412</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>1.20047393364928</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>31.225806451612801</v>
+      </c>
+      <c r="E16">
+        <v>0.45403377110693971</v>
+      </c>
+      <c r="F16">
+        <v>-0.34291184304614308</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>1.4020537124802499</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>42.580645161290299</v>
+      </c>
+      <c r="E17">
+        <v>0.74157303370786443</v>
+      </c>
+      <c r="F17">
+        <v>-0.12984607110304461</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>1.6018957345971501</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18">
+        <v>52.129032258064498</v>
+      </c>
+      <c r="E18">
+        <v>1.0889487870619941</v>
+      </c>
+      <c r="F18">
+        <v>3.7007455495558783E-2</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>0.75</v>
+      </c>
+      <c r="B19">
+        <v>0.76951026856240101</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>19.612903225806399</v>
+      </c>
+      <c r="E19">
+        <v>0.24398073836275999</v>
+      </c>
+      <c r="F19">
+        <v>-0.61264445871439843</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0.75</v>
+      </c>
+      <c r="B20">
+        <v>0.87725118483412301</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>28.129032258064498</v>
+      </c>
+      <c r="E20">
+        <v>0.3913824057450625</v>
+      </c>
+      <c r="F20">
+        <v>-0.40739870156912439</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0.75</v>
+      </c>
+      <c r="B21">
+        <v>1.25608214849921</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>41.0322580645161</v>
+      </c>
+      <c r="E21">
+        <v>0.69584245076586348</v>
+      </c>
+      <c r="F21">
+        <v>-0.15748908008541809</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>0.75</v>
+      </c>
+      <c r="B22">
+        <v>1.4037914691943101</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>52.645161290322498</v>
+      </c>
+      <c r="E22">
+        <v>1.111716621253402</v>
+      </c>
+      <c r="F22">
+        <v>4.5994098837789217E-2</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>0.75</v>
+      </c>
+      <c r="B23">
+        <v>1.56887835703001</v>
+      </c>
+      <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>59.096774193548299</v>
+      </c>
+      <c r="E23">
+        <v>1.444794952681383</v>
+      </c>
+      <c r="F23">
+        <v>0.15980621578611609</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>0.5</v>
+      </c>
+      <c r="B24">
+        <v>0.74865718799367997</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24">
+        <v>25.5483870967741</v>
+      </c>
+      <c r="E24">
+        <v>0.3431542461005182</v>
+      </c>
+      <c r="F24">
+        <v>-0.46451062289420247</v>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>0.5</v>
+      </c>
+      <c r="B25">
+        <v>0.90157977883096296</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>36.903225806451601</v>
+      </c>
+      <c r="E25">
+        <v>0.58486707566462137</v>
+      </c>
+      <c r="F25">
+        <v>-0.2329428259945775</v>
+      </c>
+      <c r="G25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>0.5</v>
+      </c>
+      <c r="B26">
+        <v>1.20047393364928</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>47.4838709677419</v>
+      </c>
+      <c r="E26">
+        <v>0.90417690417690288</v>
+      </c>
+      <c r="F26">
+        <v>-4.3746590551702998E-2</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>0.5</v>
+      </c>
+      <c r="B27">
+        <v>1.4003159557661899</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>62.193548387096698</v>
+      </c>
+      <c r="E27">
+        <v>1.6450511945392441</v>
+      </c>
+      <c r="F27">
+        <v>0.21617941788473871</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>0.5</v>
+      </c>
+      <c r="B28">
+        <v>1.6001579778830901</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>73.0322580645161</v>
+      </c>
+      <c r="E28">
+        <v>2.7081339712918622</v>
+      </c>
+      <c r="F28">
+        <v>0.43267014507721679</v>
+      </c>
+      <c r="G28">
+        <v>8</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B29" s="7">
+        <v>0.73475513428119998</v>
+      </c>
+      <c r="C29" s="7">
+        <v>5</v>
+      </c>
+      <c r="D29" s="7">
+        <v>33.5483870967741</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.50485436893203661</v>
+      </c>
+      <c r="F29" s="7">
+        <v>-0.29683388107037489</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B30" s="7">
+        <v>0.90157977883096296</v>
+      </c>
+      <c r="C30" s="7">
+        <v>5</v>
+      </c>
+      <c r="D30" s="7">
+        <v>45.935483870967701</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.84964200477326834</v>
+      </c>
+      <c r="F30" s="7">
+        <v>-7.0764024993420827E-2</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B31" s="7">
+        <v>1.1170616113744001</v>
+      </c>
+      <c r="C31" s="7">
+        <v>5</v>
+      </c>
+      <c r="D31" s="7">
+        <v>55.741935483870897</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.259475218658888</v>
+      </c>
+      <c r="F31" s="7">
+        <v>0.1001896267721403</v>
+      </c>
+      <c r="G31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B32" s="7">
+        <v>1.38988941548183</v>
+      </c>
+      <c r="C32" s="7">
+        <v>5</v>
+      </c>
+      <c r="D32" s="7">
+        <v>72.516129032257993</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.6384976525821502</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0.42135671213032178</v>
+      </c>
+      <c r="G32">
+        <v>8</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B33" s="7">
+        <v>1.57930489731437</v>
+      </c>
+      <c r="C33" s="7">
+        <v>5</v>
+      </c>
+      <c r="D33" s="7">
+        <v>83.354838709677395</v>
+      </c>
+      <c r="E33" s="7">
+        <v>5.0077519379844873</v>
+      </c>
+      <c r="F33" s="7">
+        <v>0.69964280769583431</v>
+      </c>
+      <c r="G33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>0</v>
+      </c>
+      <c r="B34" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>8.43</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.27618215572785848</v>
+      </c>
+      <c r="F34" s="7">
+        <v>-0.55880438484237782</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>0</v>
+      </c>
+      <c r="B35" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2</v>
+      </c>
+      <c r="D35" s="7">
+        <v>15.59</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.55408126999170715</v>
+      </c>
+      <c r="F35" s="7">
+        <v>-0.25642653036117807</v>
+      </c>
+      <c r="G35">
+        <v>8</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>0</v>
+      </c>
+      <c r="B36" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C36" s="7">
+        <v>3</v>
+      </c>
+      <c r="D36" s="7">
+        <v>20.18</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.75845652718616896</v>
+      </c>
+      <c r="F36" s="7">
+        <v>-0.12006930682745021</v>
+      </c>
+      <c r="G36">
+        <v>8</v>
+      </c>
+      <c r="H36" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>0</v>
+      </c>
+      <c r="B37" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C37" s="7">
+        <v>4</v>
+      </c>
+      <c r="D37" s="7">
+        <v>28.24</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.1806020066889631</v>
+      </c>
+      <c r="F37" s="7">
+        <v>7.2103517063392866E-2</v>
+      </c>
+      <c r="G37">
+        <v>8</v>
+      </c>
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>0</v>
+      </c>
+      <c r="B38" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C38" s="7">
+        <v>5</v>
+      </c>
+      <c r="D38" s="7">
+        <v>38.65</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.889975550122249</v>
+      </c>
+      <c r="F38" s="7">
+        <v>0.27645618591098309</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H43" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -3439,38 +5818,44 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="P1" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>59</v>
+      </c>
+      <c r="S1" t="s">
+        <v>60</v>
+      </c>
+      <c r="T1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>4.9878531370748496</v>
       </c>
       <c r="B2">
@@ -3495,42 +5880,26 @@
         <v>-1.74</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>-1.36</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <f t="shared" ref="T2:T19" si="0">10^(-B2)</f>
-        <v>0.57411646220732748</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="1">
         <v>4.9785421780668777</v>
       </c>
       <c r="B3">
@@ -3555,16 +5924,16 @@
         <v>-1.47</v>
       </c>
       <c r="I3">
-        <v>-1.53</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -3572,25 +5941,9 @@
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <f t="shared" si="0"/>
-        <v>0.29716660317380256</v>
-      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="1">
         <v>4.9294758200052957</v>
       </c>
       <c r="B4">
@@ -3615,10 +5968,10 @@
         <v>-0.98</v>
       </c>
       <c r="I4">
-        <v>-1.53</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>-1.46</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -3632,25 +5985,9 @@
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <f t="shared" si="0"/>
-        <v>0.15995580286146685</v>
-      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="1">
         <v>4.8132193011041764</v>
       </c>
       <c r="B5">
@@ -3675,42 +6012,26 @@
         <v>-0.24</v>
       </c>
       <c r="I5">
-        <v>-1.53</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>-1.44</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="0"/>
-        <v>7.2945751025456848E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="1">
         <v>4.751685080492198</v>
       </c>
       <c r="B6">
@@ -3735,10 +6056,10 @@
         <v>0.26</v>
       </c>
       <c r="I6">
-        <v>-1.22</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>-1.32</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3752,25 +6073,9 @@
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="0"/>
-        <v>4.7752927365769082E-2</v>
-      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="1">
         <v>4.7231095025915941</v>
       </c>
       <c r="B7">
@@ -3795,10 +6100,10 @@
         <v>0.61</v>
       </c>
       <c r="I7">
-        <v>-1.22</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>-1.19</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3812,25 +6117,9 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="0"/>
-        <v>3.4197944251370883E-2</v>
-      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="1">
         <v>4.7094378121328804</v>
       </c>
       <c r="B8">
@@ -3855,42 +6144,26 @@
         <v>0.77</v>
       </c>
       <c r="I8">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="0"/>
-        <v>2.9922646366081884E-2</v>
-      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>1.9915790348048139</v>
       </c>
       <c r="B9">
@@ -3915,10 +6188,10 @@
         <v>-1.741725335781714</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -3927,30 +6200,32 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.3736263736263585</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>1.3846153846153493</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.7802197802197592</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.3846153846153493</v>
+      </c>
+      <c r="S9">
+        <v>2.1758241758241397</v>
       </c>
       <c r="T9">
-        <f t="shared" si="0"/>
-        <v>0.5812775655381871</v>
+        <v>1.7802197802197592</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10">
         <v>1.980691304582046</v>
       </c>
       <c r="B10">
@@ -3975,10 +6250,10 @@
         <v>-1.514596939418587</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -3993,24 +6268,26 @@
         <v>1</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>6.329670329670317</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>3.3626373626373383</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.9670329670329285</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.571428571428549</v>
+      </c>
+      <c r="S10">
+        <v>2.571428571428549</v>
       </c>
       <c r="T10">
-        <f t="shared" si="0"/>
-        <v>0.29595990327355498</v>
+        <v>2.9670329670329285</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>1.9336677366397059</v>
       </c>
       <c r="B11">
@@ -4035,10 +6312,10 @@
         <v>-0.95957134294439284</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4053,24 +6330,26 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>25.912087912087795</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>3.1648351648351496</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.3626373626373383</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.7692307692307394</v>
+      </c>
+      <c r="S11">
+        <v>3.56043956043953</v>
       </c>
       <c r="T11">
-        <f t="shared" si="0"/>
-        <v>0.15749264397861987</v>
+        <v>9.8901098901098674</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>1.827040781438199</v>
       </c>
       <c r="B12">
@@ -4095,42 +6374,44 @@
         <v>-0.24615343666192119</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>68.637362637362614</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.1538461538461409</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.56043956043953</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.571428571428549</v>
+      </c>
+      <c r="S12">
+        <v>6.7252747252746978</v>
       </c>
       <c r="T12">
-        <f t="shared" si="0"/>
-        <v>6.8057612907559836E-2</v>
+        <v>36.197802197802098</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+      <c r="A13">
         <v>1.7705451871527289</v>
       </c>
       <c r="B13">
@@ -4155,10 +6436,10 @@
         <v>0.25527250510330463</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -4173,24 +6454,26 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>87.428571428571402</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>4.7472527472527402</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.5494505494505493</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>7.5164835164834978</v>
+      </c>
+      <c r="S13">
+        <v>13.846153846153793</v>
       </c>
       <c r="T13">
-        <f t="shared" si="0"/>
-        <v>3.833201450680674E-2</v>
+        <v>64.285714285714207</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>1.7440974190635239</v>
       </c>
       <c r="B14">
@@ -4215,10 +6498,10 @@
         <v>0.59434585455452171</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -4233,24 +6516,26 @@
         <v>1</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>93.956043956043899</v>
       </c>
       <c r="P14">
-        <v>1</v>
+        <v>6.5274725274725096</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>6.1318681318681314</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>12.659340659340595</v>
+      </c>
+      <c r="S14">
+        <v>23.340659340659293</v>
       </c>
       <c r="T14">
-        <f t="shared" si="0"/>
-        <v>2.4338923735390913E-2</v>
+        <v>79.714285714285694</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>1.7322008018720709</v>
       </c>
       <c r="B15">
@@ -4275,42 +6560,44 @@
         <v>0.76199725943106256</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>95.538461538461505</v>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>9.0989010989010772</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>9.0989010989010772</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>16.219780219780201</v>
+      </c>
+      <c r="S15">
+        <v>31.450549450549399</v>
       </c>
       <c r="T15">
-        <f t="shared" si="0"/>
-        <v>2.0142324533150509E-2</v>
+        <v>85.252747252747199</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>1.7069872080419219</v>
       </c>
       <c r="B16">
@@ -4335,10 +6622,10 @@
         <v>1.206967825528747</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -4353,200 +6640,22 @@
         <v>1</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>98.505494505494497</v>
       </c>
       <c r="P16">
-        <v>1</v>
+        <v>10.087912087911995</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>10.681318681318601</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>30.857142857142801</v>
+      </c>
+      <c r="S16">
+        <v>55.978021978021907</v>
       </c>
       <c r="T16">
-        <f t="shared" si="0"/>
-        <v>8.4338796081341733E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>25</v>
-      </c>
-      <c r="B17">
-        <v>1.5</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>-0.26750963699125352</v>
-      </c>
-      <c r="E17">
-        <v>-5.5316923634942707E-2</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>-0.20910908521850771</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>-0.61134831389953581</v>
-      </c>
-      <c r="J17">
-        <v>-1.7026524217189538E-2</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="0"/>
-        <v>3.1622776601683784E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>25</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0.25573196162710737</v>
-      </c>
-      <c r="E18">
-        <v>0.54236684047993289</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>-3.1804562525097141E-2</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>-0.1512553277727009</v>
-      </c>
-      <c r="J18">
-        <v>0.21796179846852079</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>2.5</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0.29563415617744288</v>
-      </c>
-      <c r="E19">
-        <v>0.54866024026583626</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>-3.076090305997338E-2</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>-9.1714900819881665E-2</v>
-      </c>
-      <c r="J19">
-        <v>0.50346445715765153</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="0"/>
-        <v>3.1622776601683764E-3</v>
+        <v>94.153846153846104</v>
       </c>
     </row>
   </sheetData>
@@ -4555,6 +6664,1536 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>4.9878531370748496</v>
+      </c>
+      <c r="B2" s="7">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="C2" s="7">
+        <v>-1.64</v>
+      </c>
+      <c r="D2">
+        <v>-1.36</v>
+      </c>
+      <c r="E2" s="7">
+        <v>-1.81</v>
+      </c>
+      <c r="F2" s="7">
+        <v>-1.67</v>
+      </c>
+      <c r="G2" s="7">
+        <v>-1.85</v>
+      </c>
+      <c r="H2" s="7">
+        <v>-1.74</v>
+      </c>
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>-1.36</v>
+      </c>
+      <c r="K2" s="7">
+        <v>10</v>
+      </c>
+      <c r="L2" s="7">
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>10</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7">
+        <v>10</v>
+      </c>
+      <c r="P2" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+      <c r="S2" s="7">
+        <v>2.2395622457170412</v>
+      </c>
+      <c r="T2" s="7">
+        <v>4.1825819962989419</v>
+      </c>
+      <c r="U2" s="7">
+        <v>2.0932100521339581</v>
+      </c>
+      <c r="V2" s="7">
+        <v>1.3928628341453531</v>
+      </c>
+      <c r="W2" s="7">
+        <v>1.7871795372261761</v>
+      </c>
+      <c r="X2" s="7">
+        <v>1.4909941389328649</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>1.1879817525171541</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>1.5251941583177719</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>4.9785421780668777</v>
+      </c>
+      <c r="B3">
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="C3">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="D3">
+        <v>-1.48</v>
+      </c>
+      <c r="E3">
+        <v>-1.54</v>
+      </c>
+      <c r="F3">
+        <v>-1.62</v>
+      </c>
+      <c r="G3">
+        <v>-1.59</v>
+      </c>
+      <c r="H3">
+        <v>-1.47</v>
+      </c>
+      <c r="I3">
+        <v>-1.53</v>
+      </c>
+      <c r="J3">
+        <v>-1.2</v>
+      </c>
+      <c r="K3" s="7">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>10</v>
+      </c>
+      <c r="O3" s="7">
+        <v>10</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>6.6114061337195604</v>
+      </c>
+      <c r="T3">
+        <v>3.205177802787111</v>
+      </c>
+      <c r="U3">
+        <v>2.803186715169653</v>
+      </c>
+      <c r="V3">
+        <v>2.3426369721582359</v>
+      </c>
+      <c r="W3">
+        <v>2.5059821239382138</v>
+      </c>
+      <c r="X3">
+        <v>3.2773891454587498</v>
+      </c>
+      <c r="Y3">
+        <v>2.866609580241787</v>
+      </c>
+      <c r="Z3">
+        <v>5.9350943102767584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>4.9294758200052957</v>
+      </c>
+      <c r="B4">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="C4">
+        <v>-0.46</v>
+      </c>
+      <c r="D4">
+        <v>-1.51</v>
+      </c>
+      <c r="E4">
+        <v>-1.46</v>
+      </c>
+      <c r="F4">
+        <v>-1.55</v>
+      </c>
+      <c r="G4">
+        <v>-1.42</v>
+      </c>
+      <c r="H4">
+        <v>-0.98</v>
+      </c>
+      <c r="I4">
+        <v>-1.53</v>
+      </c>
+      <c r="J4">
+        <v>-1.46</v>
+      </c>
+      <c r="K4" s="7">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4" s="7">
+        <v>10</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>5</v>
+      </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4">
+        <v>25.746444105693019</v>
+      </c>
+      <c r="T4">
+        <v>2.9976589159516012</v>
+      </c>
+      <c r="U4">
+        <v>3.351171054837125</v>
+      </c>
+      <c r="V4">
+        <v>2.7411274627306499</v>
+      </c>
+      <c r="W4">
+        <v>3.6626441176046929</v>
+      </c>
+      <c r="X4">
+        <v>9.4787395973196098</v>
+      </c>
+      <c r="Y4">
+        <v>2.866609580241787</v>
+      </c>
+      <c r="Z4">
+        <v>3.3511710548371201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>4.8132193011041764</v>
+      </c>
+      <c r="B5" s="10">
+        <v>1.137</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="D5">
+        <v>-1.34</v>
+      </c>
+      <c r="E5" s="10">
+        <v>-1.44</v>
+      </c>
+      <c r="F5" s="10">
+        <v>-1.55</v>
+      </c>
+      <c r="G5" s="10">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="H5" s="10">
+        <v>-0.24</v>
+      </c>
+      <c r="I5" s="10">
+        <v>-1.53</v>
+      </c>
+      <c r="J5" s="10">
+        <v>-1.44</v>
+      </c>
+      <c r="K5" s="7">
+        <v>5</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>10</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>5</v>
+      </c>
+      <c r="S5" s="10">
+        <v>69.123615241476301</v>
+      </c>
+      <c r="T5" s="10">
+        <v>4.3710847735683966</v>
+      </c>
+      <c r="U5" s="10">
+        <v>3.5035734831986272</v>
+      </c>
+      <c r="V5" s="10">
+        <v>2.7411274627306499</v>
+      </c>
+      <c r="W5" s="10">
+        <v>6.4706500953921759</v>
+      </c>
+      <c r="X5" s="10">
+        <v>36.525666494768323</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>2.866609580241787</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>6.7550028996576179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>4.751685080492198</v>
+      </c>
+      <c r="B6">
+        <v>1.321</v>
+      </c>
+      <c r="C6">
+        <v>0.87</v>
+      </c>
+      <c r="D6">
+        <v>-1.3</v>
+      </c>
+      <c r="E6">
+        <v>-1.32</v>
+      </c>
+      <c r="F6">
+        <v>-1.1100000000000001</v>
+      </c>
+      <c r="G6">
+        <v>-0.8</v>
+      </c>
+      <c r="H6">
+        <v>0.26</v>
+      </c>
+      <c r="I6">
+        <v>-1.22</v>
+      </c>
+      <c r="J6">
+        <v>-1.32</v>
+      </c>
+      <c r="K6" s="7">
+        <v>5</v>
+      </c>
+      <c r="L6" s="10">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>5</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>88.113778355369817</v>
+      </c>
+      <c r="T6">
+        <v>4.7726721034203887</v>
+      </c>
+      <c r="U6">
+        <v>4.5676781039662373</v>
+      </c>
+      <c r="V6">
+        <v>7.2033158503842589</v>
+      </c>
+      <c r="W6">
+        <v>13.680688860321</v>
+      </c>
+      <c r="X6">
+        <v>64.535245043938247</v>
+      </c>
+      <c r="Y6">
+        <v>5.6831520840097216</v>
+      </c>
+      <c r="Z6">
+        <v>4.1825819962989419</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>4.7231095025915941</v>
+      </c>
+      <c r="B7">
+        <v>1.466</v>
+      </c>
+      <c r="C7">
+        <v>1.2</v>
+      </c>
+      <c r="D7">
+        <v>-1.17</v>
+      </c>
+      <c r="E7">
+        <v>-1.19</v>
+      </c>
+      <c r="F7">
+        <v>-0.85</v>
+      </c>
+      <c r="G7">
+        <v>-0.52</v>
+      </c>
+      <c r="H7">
+        <v>0.61</v>
+      </c>
+      <c r="I7">
+        <v>-1.22</v>
+      </c>
+      <c r="J7">
+        <v>-1.19</v>
+      </c>
+      <c r="K7" s="7">
+        <v>5</v>
+      </c>
+      <c r="L7" s="10">
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>10</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7">
+        <v>94.064905689723247</v>
+      </c>
+      <c r="T7">
+        <v>6.3326875310947912</v>
+      </c>
+      <c r="U7">
+        <v>6.0649558509397794</v>
+      </c>
+      <c r="V7">
+        <v>12.377068106893541</v>
+      </c>
+      <c r="W7">
+        <v>23.194799683241602</v>
+      </c>
+      <c r="X7">
+        <v>80.290917015381595</v>
+      </c>
+      <c r="Y7">
+        <v>5.6831520840097216</v>
+      </c>
+      <c r="Z7">
+        <v>10.08826283567233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>4.7094378121328804</v>
+      </c>
+      <c r="B8">
+        <v>1.524</v>
+      </c>
+      <c r="C8">
+        <v>1.35</v>
+      </c>
+      <c r="D8">
+        <v>-1.02</v>
+      </c>
+      <c r="E8">
+        <v>-1</v>
+      </c>
+      <c r="F8">
+        <v>-0.72</v>
+      </c>
+      <c r="G8">
+        <v>-0.34</v>
+      </c>
+      <c r="H8">
+        <v>0.77</v>
+      </c>
+      <c r="I8">
+        <v>0.89</v>
+      </c>
+      <c r="J8">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="7">
+        <v>5</v>
+      </c>
+      <c r="L8" s="10">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>10</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8">
+        <v>95.724158885346398</v>
+      </c>
+      <c r="T8">
+        <v>8.7174188254586831</v>
+      </c>
+      <c r="U8">
+        <v>9.0909090909090917</v>
+      </c>
+      <c r="V8">
+        <v>16.00493053652465</v>
+      </c>
+      <c r="W8">
+        <v>31.369974231668749</v>
+      </c>
+      <c r="X8">
+        <v>85.482917753175954</v>
+      </c>
+      <c r="Y8">
+        <v>11.41230574141505</v>
+      </c>
+      <c r="Z8">
+        <v>11.647171194356069</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>1.9915790348048139</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0.235616438356164</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1.614154798725508</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-1.852615520079504</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.741725335781714</v>
+      </c>
+      <c r="F9" s="7">
+        <v>-1.852615520079504</v>
+      </c>
+      <c r="G9" s="7">
+        <v>-1.65282239968498</v>
+      </c>
+      <c r="H9" s="7">
+        <v>-1.741725335781714</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>10</v>
+      </c>
+      <c r="M9" s="7">
+        <v>10</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7">
+        <v>2.3736263736263585</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1.3846153846153493</v>
+      </c>
+      <c r="U9" s="7">
+        <v>1.7802197802197592</v>
+      </c>
+      <c r="V9" s="7">
+        <v>1.3846153846153493</v>
+      </c>
+      <c r="W9" s="7">
+        <v>2.1758241758241397</v>
+      </c>
+      <c r="X9" s="7">
+        <v>1.7802197802197592</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>1.980691304582046</v>
+      </c>
+      <c r="B10">
+        <v>0.52876712328767095</v>
+      </c>
+      <c r="C10">
+        <v>-1.1702209576189531</v>
+      </c>
+      <c r="D10">
+        <v>-1.45846503480211</v>
+      </c>
+      <c r="E10">
+        <v>-1.514596939418587</v>
+      </c>
+      <c r="F10">
+        <v>-1.578511869553177</v>
+      </c>
+      <c r="G10">
+        <v>-1.578511869553177</v>
+      </c>
+      <c r="H10">
+        <v>-1.514596939418587</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
+      </c>
+      <c r="L10" s="10">
+        <v>10</v>
+      </c>
+      <c r="M10" s="7">
+        <v>10</v>
+      </c>
+      <c r="N10">
+        <v>10</v>
+      </c>
+      <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>6.329670329670317</v>
+      </c>
+      <c r="T10">
+        <v>3.3626373626373383</v>
+      </c>
+      <c r="U10">
+        <v>2.9670329670329285</v>
+      </c>
+      <c r="V10">
+        <v>2.571428571428549</v>
+      </c>
+      <c r="W10">
+        <v>2.571428571428549</v>
+      </c>
+      <c r="X10">
+        <v>2.9670329670329285</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>1.9336677366397059</v>
+      </c>
+      <c r="B11">
+        <v>0.80273972602739696</v>
+      </c>
+      <c r="C11">
+        <v>-0.45624494742588528</v>
+      </c>
+      <c r="D11">
+        <v>-1.4856820007195011</v>
+      </c>
+      <c r="E11">
+        <v>-1.45846503480211</v>
+      </c>
+      <c r="F11">
+        <v>-1.545444573179084</v>
+      </c>
+      <c r="G11">
+        <v>-1.4327516043600459</v>
+      </c>
+      <c r="H11">
+        <v>-0.95957134294439284</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>25.912087912087799</v>
+      </c>
+      <c r="T11" s="11">
+        <v>3.1648351648351496</v>
+      </c>
+      <c r="U11">
+        <v>3.3626373626373383</v>
+      </c>
+      <c r="V11">
+        <v>2.7692307692307394</v>
+      </c>
+      <c r="W11">
+        <v>3.56043956043953</v>
+      </c>
+      <c r="X11">
+        <v>9.8901098901098674</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>1.827040781438199</v>
+      </c>
+      <c r="B12" s="10">
+        <v>1.1671232876712301</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0.34014801111555087</v>
+      </c>
+      <c r="D12" s="10">
+        <v>-1.3631242825001839</v>
+      </c>
+      <c r="E12" s="10">
+        <v>-1.4327516043600459</v>
+      </c>
+      <c r="F12" s="10">
+        <v>-1.578511869553177</v>
+      </c>
+      <c r="G12" s="10">
+        <v>-1.142053948747725</v>
+      </c>
+      <c r="H12" s="10">
+        <v>-0.24615343666192119</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>5</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
+        <v>0</v>
+      </c>
+      <c r="S12" s="10">
+        <v>68.637362637362614</v>
+      </c>
+      <c r="T12" s="10">
+        <v>4.1538461538461409</v>
+      </c>
+      <c r="U12" s="10">
+        <v>3.56043956043953</v>
+      </c>
+      <c r="V12" s="10">
+        <v>2.571428571428549</v>
+      </c>
+      <c r="W12" s="10">
+        <v>6.7252747252746978</v>
+      </c>
+      <c r="X12" s="10">
+        <v>36.197802197802098</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>1.7705451871527289</v>
+      </c>
+      <c r="B13">
+        <v>1.4164383561643801</v>
+      </c>
+      <c r="C13">
+        <v>0.84226874999539159</v>
+      </c>
+      <c r="D13">
+        <v>-1.3024351558328691</v>
+      </c>
+      <c r="E13">
+        <v>-1.321819483905311</v>
+      </c>
+      <c r="F13">
+        <v>-1.0900496250895491</v>
+      </c>
+      <c r="G13">
+        <v>-0.79394551756687726</v>
+      </c>
+      <c r="H13">
+        <v>0.25527250510330463</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>5</v>
+      </c>
+      <c r="L13">
+        <v>10</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>5</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>87.428571428571402</v>
+      </c>
+      <c r="T13">
+        <v>4.7472527472527402</v>
+      </c>
+      <c r="U13">
+        <v>4.5494505494505493</v>
+      </c>
+      <c r="V13">
+        <v>7.5164835164834978</v>
+      </c>
+      <c r="W13">
+        <v>13.846153846153793</v>
+      </c>
+      <c r="X13">
+        <v>64.285714285714207</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>1.7440974190635239</v>
+      </c>
+      <c r="B14">
+        <v>1.61369863013698</v>
+      </c>
+      <c r="C14">
+        <v>1.191603425233924</v>
+      </c>
+      <c r="D14">
+        <v>-1.155938933396812</v>
+      </c>
+      <c r="E14">
+        <v>-1.184925368153227</v>
+      </c>
+      <c r="F14">
+        <v>-0.83880537935058663</v>
+      </c>
+      <c r="G14">
+        <v>-0.51645195951508038</v>
+      </c>
+      <c r="H14">
+        <v>0.59434585455452171</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>5</v>
+      </c>
+      <c r="L14">
+        <v>10</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>10</v>
+      </c>
+      <c r="O14">
+        <v>5</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>93.956043956043899</v>
+      </c>
+      <c r="T14">
+        <v>6.5274725274725096</v>
+      </c>
+      <c r="U14">
+        <v>6.1318681318681314</v>
+      </c>
+      <c r="V14">
+        <v>12.659340659340595</v>
+      </c>
+      <c r="W14">
+        <v>23.340659340659293</v>
+      </c>
+      <c r="X14">
+        <v>79.714285714285694</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>1.7322008018720709</v>
+      </c>
+      <c r="B15">
+        <v>1.6958904109588999</v>
+      </c>
+      <c r="C15">
+        <v>1.330693602277621</v>
+      </c>
+      <c r="D15">
+        <v>-0.99958018896498813</v>
+      </c>
+      <c r="E15">
+        <v>-0.99958018896498813</v>
+      </c>
+      <c r="F15">
+        <v>-0.71309653014324781</v>
+      </c>
+      <c r="G15">
+        <v>-0.33837574099736839</v>
+      </c>
+      <c r="H15">
+        <v>0.76199725943106256</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <v>5</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>95.538461538461505</v>
+      </c>
+      <c r="T15">
+        <v>9.0989010989010772</v>
+      </c>
+      <c r="U15">
+        <v>9.0989010989010772</v>
+      </c>
+      <c r="V15">
+        <v>16.219780219780201</v>
+      </c>
+      <c r="W15">
+        <v>31.450549450549399</v>
+      </c>
+      <c r="X15">
+        <v>85.252747252747199</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>1.7069872080419219</v>
+      </c>
+      <c r="B16">
+        <v>2.0739726027397198</v>
+      </c>
+      <c r="C16">
+        <v>1.818962939492804</v>
+      </c>
+      <c r="D16">
+        <v>-0.95001679396111671</v>
+      </c>
+      <c r="E16">
+        <v>-0.92231743001357314</v>
+      </c>
+      <c r="F16">
+        <v>-0.35039161049348272</v>
+      </c>
+      <c r="G16">
+        <v>0.1043479956700375</v>
+      </c>
+      <c r="H16">
+        <v>1.206967825528747</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16">
+        <v>10</v>
+      </c>
+      <c r="O16">
+        <v>5</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>98.505494505494497</v>
+      </c>
+      <c r="T16">
+        <v>10.087912087911995</v>
+      </c>
+      <c r="U16">
+        <v>10.681318681318601</v>
+      </c>
+      <c r="V16">
+        <v>30.857142857142801</v>
+      </c>
+      <c r="W16">
+        <v>55.978021978021907</v>
+      </c>
+      <c r="X16">
+        <v>94.153846153846104</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>25</v>
+      </c>
+      <c r="B17">
+        <v>1.5</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>-0.26750963699125352</v>
+      </c>
+      <c r="E17">
+        <v>-5.5316923634942707E-2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>-0.20910908521850771</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>-0.61134831389953581</v>
+      </c>
+      <c r="J17">
+        <v>-1.7026524217189538E-2</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>5</v>
+      </c>
+      <c r="M17">
+        <v>5</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>5</v>
+      </c>
+      <c r="R17">
+        <v>5</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>35.07</v>
+      </c>
+      <c r="U17">
+        <v>46.82</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>38.19</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>19.66</v>
+      </c>
+      <c r="Z17">
+        <v>49.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.25573196162710737</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.54236684047993289</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>-3.1804562525097141E-2</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>-0.1512553277727009</v>
+      </c>
+      <c r="J18" s="7">
+        <v>0.21796179846852079</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>5</v>
+      </c>
+      <c r="M18">
+        <v>5</v>
+      </c>
+      <c r="N18" s="7">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>5</v>
+      </c>
+      <c r="R18">
+        <v>5</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0</v>
+      </c>
+      <c r="T18" s="7">
+        <v>64.31</v>
+      </c>
+      <c r="U18" s="7">
+        <v>77.709999999999994</v>
+      </c>
+      <c r="V18" s="7">
+        <v>0</v>
+      </c>
+      <c r="W18" s="7">
+        <v>48.17</v>
+      </c>
+      <c r="X18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="7">
+        <v>41.38</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>62.29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <v>2.5</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0.29563415617744288</v>
+      </c>
+      <c r="E19">
+        <v>0.54866024026583626</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>-3.076090305997338E-2</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>-9.1714900819881665E-2</v>
+      </c>
+      <c r="J19">
+        <v>0.50346445715765153</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>5</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" s="7">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>5</v>
+      </c>
+      <c r="R19">
+        <v>5</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>66.39</v>
+      </c>
+      <c r="U19">
+        <v>77.959999999999994</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>48.23</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>44.74</v>
+      </c>
+      <c r="Z19">
+        <v>76.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5631,7 +9270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6197,7 +9836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6441,7 +10080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6567,7 +10206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6693,7 +10332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6817,366 +10456,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0.5</v>
-      </c>
-      <c r="C2">
-        <v>0.37890162349538931</v>
-      </c>
-      <c r="D2">
-        <v>-0.55880438484237782</v>
-      </c>
-      <c r="E2">
-        <v>-0.22018318867981981</v>
-      </c>
-      <c r="F2">
-        <v>0.28887120618536088</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0.5</v>
-      </c>
-      <c r="C3">
-        <v>0.74730347581587131</v>
-      </c>
-      <c r="D3">
-        <v>-0.25642653036117807</v>
-      </c>
-      <c r="E3">
-        <v>-9.619521531998218E-2</v>
-      </c>
-      <c r="F3">
-        <v>0.41814043679433921</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0.5</v>
-      </c>
-      <c r="C4">
-        <v>0.81772606167682238</v>
-      </c>
-      <c r="D4">
-        <v>-0.12006930682745021</v>
-      </c>
-      <c r="E4">
-        <v>-1.048649293295891E-2</v>
-      </c>
-      <c r="F4">
-        <v>0.47260455139702251</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0.5</v>
-      </c>
-      <c r="C5">
-        <v>0.94732133535924345</v>
-      </c>
-      <c r="D5">
-        <v>7.2103517063392866E-2</v>
-      </c>
-      <c r="E5">
-        <v>0.15970084286751191</v>
-      </c>
-      <c r="F5">
-        <v>0.52895058389195404</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0.5</v>
-      </c>
-      <c r="C6">
-        <v>1.00311120790082</v>
-      </c>
-      <c r="D6">
-        <v>0.27645618591098309</v>
-      </c>
-      <c r="E6">
-        <v>0.2413180682920206</v>
-      </c>
-      <c r="F6">
-        <v>0.63375355796501509</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>0.19</v>
-      </c>
-      <c r="C7">
-        <v>0.2019624381862466</v>
-      </c>
-      <c r="D7">
-        <v>0.73398894149761618</v>
-      </c>
-      <c r="E7">
-        <v>2.2411320697578532E-2</v>
-      </c>
-      <c r="F7">
-        <v>0.37467651080669062</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>0.5</v>
-      </c>
-      <c r="C8">
-        <v>0.76789849152443013</v>
-      </c>
-      <c r="D8">
-        <v>-0.26172914980845402</v>
-      </c>
-      <c r="E8">
-        <v>-9.0732996238242117E-2</v>
-      </c>
-      <c r="F8">
-        <v>0.41866397556212759</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>0.99</v>
-      </c>
-      <c r="C9">
-        <v>1.224347751283891</v>
-      </c>
-      <c r="D9">
-        <v>-0.60959581881686786</v>
-      </c>
-      <c r="E9">
-        <v>-0.23437228355177231</v>
-      </c>
-      <c r="F9">
-        <v>0.46721891154789469</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>1.49</v>
-      </c>
-      <c r="C10">
-        <v>1.78025349022115</v>
-      </c>
-      <c r="D10">
-        <v>-0.65230372820996729</v>
-      </c>
-      <c r="E10">
-        <v>-0.52714761933160048</v>
-      </c>
-      <c r="F10">
-        <v>0.60236401267877693</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>1.79</v>
-      </c>
-      <c r="C11">
-        <v>1.9074053552227761</v>
-      </c>
-      <c r="D11">
-        <v>-1.574557366498176</v>
-      </c>
-      <c r="E11">
-        <v>-0.56219097385209027</v>
-      </c>
-      <c r="F11">
-        <v>0.8488269794820742</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/prommis/solvent_extraction/data for parmest.xlsx
+++ b/src/prommis/solvent_extraction/data for parmest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ad00105\Desktop\Model_software\prommis\src\prommis\solvent_extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D820306-4312-4B73-B1B7-10239D8CC8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FB0F5A-EA5E-4948-8A0D-1AD4276BC429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="1785" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="1785" windowWidth="25440" windowHeight="15270" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2 (2)" sheetId="14" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="new parameter values" sheetId="11" r:id="rId12"/>
     <sheet name="Fe only" sheetId="12" r:id="rId13"/>
     <sheet name="Fe only (2)" sheetId="13" r:id="rId14"/>
+    <sheet name="Fe only (3)" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="65">
   <si>
     <t>dosage</t>
   </si>
@@ -5787,6 +5788,1171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4C7D81-62EA-436C-A3B6-67C7F04DA4D1}">
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1.5</v>
+      </c>
+      <c r="B2">
+        <v>0.75908372827804105</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>3.3548387096774199</v>
+      </c>
+      <c r="E2">
+        <v>3.4712950600801068E-2</v>
+      </c>
+      <c r="F2">
+        <v>-1.459508469728648</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>A2/176.12</f>
+        <v>8.5169202816261641E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1.5</v>
+      </c>
+      <c r="B3">
+        <v>0.922432859399684</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>3.87096774193548</v>
+      </c>
+      <c r="E3">
+        <v>4.0268456375838882E-2</v>
+      </c>
+      <c r="F3">
+        <v>-1.3950350180286311</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J38" si="0">A3/176.12</f>
+        <v>8.5169202816261641E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1.5</v>
+      </c>
+      <c r="B4">
+        <v>1.24391785150078</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>6.9677419354838497</v>
+      </c>
+      <c r="E4">
+        <v>7.4895977808598913E-2</v>
+      </c>
+      <c r="F4">
+        <v>-1.1255415048964621</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>8.5169202816261641E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1.5</v>
+      </c>
+      <c r="B5">
+        <v>1.4541864139020499</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>17.5483870967741</v>
+      </c>
+      <c r="E5">
+        <v>0.21283255086071851</v>
+      </c>
+      <c r="F5">
+        <v>-0.67196194978818546</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>8.5169202816261641E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1.5</v>
+      </c>
+      <c r="B6">
+        <v>1.5984202211690299</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>25.2903225806451</v>
+      </c>
+      <c r="E6">
+        <v>0.33851468048359129</v>
+      </c>
+      <c r="F6">
+        <v>-0.47042249237096162</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>8.5169202816261641E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1.5</v>
+      </c>
+      <c r="B7">
+        <v>1.81216429699842</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>32.774193548387103</v>
+      </c>
+      <c r="E7">
+        <v>0.48752399232245702</v>
+      </c>
+      <c r="F7">
+        <v>-0.31200400667958628</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>8.5169202816261641E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1.25</v>
+      </c>
+      <c r="B8">
+        <v>0.75908372827804105</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>6.9677419354838497</v>
+      </c>
+      <c r="E8">
+        <v>7.4895977808598913E-2</v>
+      </c>
+      <c r="F8">
+        <v>-1.1255415048964621</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>7.0974335680218034E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1.25</v>
+      </c>
+      <c r="B9">
+        <v>0.89810426540284305</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="F9">
+        <v>-1.060697840353612</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>7.0974335680218034E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1.25</v>
+      </c>
+      <c r="B10">
+        <v>1.23522906793048</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>20.387096774193498</v>
+      </c>
+      <c r="E10">
+        <v>0.25607779578606082</v>
+      </c>
+      <c r="F10">
+        <v>-0.59162807707882048</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>7.0974335680218034E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1.25</v>
+      </c>
+      <c r="B11">
+        <v>1.3690363349131101</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>30.451612903225701</v>
+      </c>
+      <c r="E11">
+        <v>0.43784786641929291</v>
+      </c>
+      <c r="F11">
+        <v>-0.35867676221663419</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>7.0974335680218034E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1.25</v>
+      </c>
+      <c r="B12">
+        <v>1.5897314375987299</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>39.4838709677419</v>
+      </c>
+      <c r="E12">
+        <v>0.65245202558635296</v>
+      </c>
+      <c r="F12">
+        <v>-0.18545141623350389</v>
+      </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>7.0974335680218034E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1.25</v>
+      </c>
+      <c r="B13">
+        <v>1.76524486571879</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>45.677419354838698</v>
+      </c>
+      <c r="E13">
+        <v>0.84085510688836063</v>
+      </c>
+      <c r="F13">
+        <v>-7.5278833809880707E-2</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>7.0974335680218034E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>0.75039494470774004</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>12.1290322580645</v>
+      </c>
+      <c r="E14">
+        <v>0.13803230543318629</v>
+      </c>
+      <c r="F14">
+        <v>-0.86001925831308712</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>5.6779468544174427E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>0.89984202211690301</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>20.645161290322498</v>
+      </c>
+      <c r="E15">
+        <v>0.26016260162601501</v>
+      </c>
+      <c r="F15">
+        <v>-0.58475513311949412</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>5.6779468544174427E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>1.20047393364928</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>31.225806451612801</v>
+      </c>
+      <c r="E16">
+        <v>0.45403377110693971</v>
+      </c>
+      <c r="F16">
+        <v>-0.34291184304614308</v>
+      </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>5.6779468544174427E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>1.4020537124802499</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>42.580645161290299</v>
+      </c>
+      <c r="E17">
+        <v>0.74157303370786443</v>
+      </c>
+      <c r="F17">
+        <v>-0.12984607110304461</v>
+      </c>
+      <c r="G17">
+        <v>6</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>5.6779468544174427E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>1.6018957345971501</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18">
+        <v>52.129032258064498</v>
+      </c>
+      <c r="E18">
+        <v>1.0889487870619941</v>
+      </c>
+      <c r="F18">
+        <v>3.7007455495558783E-2</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>5.6779468544174427E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>0.75</v>
+      </c>
+      <c r="B19">
+        <v>0.76951026856240101</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>19.612903225806399</v>
+      </c>
+      <c r="E19">
+        <v>0.24398073836275999</v>
+      </c>
+      <c r="F19">
+        <v>-0.61264445871439843</v>
+      </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>4.2584601408130821E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0.75</v>
+      </c>
+      <c r="B20">
+        <v>0.87725118483412301</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>28.129032258064498</v>
+      </c>
+      <c r="E20">
+        <v>0.3913824057450625</v>
+      </c>
+      <c r="F20">
+        <v>-0.40739870156912439</v>
+      </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>4.2584601408130821E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0.75</v>
+      </c>
+      <c r="B21">
+        <v>1.25608214849921</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>41.0322580645161</v>
+      </c>
+      <c r="E21">
+        <v>0.69584245076586348</v>
+      </c>
+      <c r="F21">
+        <v>-0.15748908008541809</v>
+      </c>
+      <c r="G21">
+        <v>6</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>4.2584601408130821E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>0.75</v>
+      </c>
+      <c r="B22">
+        <v>1.4037914691943101</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>52.645161290322498</v>
+      </c>
+      <c r="E22">
+        <v>1.111716621253402</v>
+      </c>
+      <c r="F22">
+        <v>4.5994098837789217E-2</v>
+      </c>
+      <c r="G22">
+        <v>6</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>4.2584601408130821E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>0.75</v>
+      </c>
+      <c r="B23">
+        <v>1.56887835703001</v>
+      </c>
+      <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>59.096774193548299</v>
+      </c>
+      <c r="E23">
+        <v>1.444794952681383</v>
+      </c>
+      <c r="F23">
+        <v>0.15980621578611609</v>
+      </c>
+      <c r="G23">
+        <v>6</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>4.2584601408130821E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>0.5</v>
+      </c>
+      <c r="B24">
+        <v>0.74865718799367997</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24">
+        <v>25.5483870967741</v>
+      </c>
+      <c r="E24">
+        <v>0.3431542461005182</v>
+      </c>
+      <c r="F24">
+        <v>-0.46451062289420247</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="0"/>
+        <v>2.8389734272087214E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>0.5</v>
+      </c>
+      <c r="B25">
+        <v>0.90157977883096296</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>36.903225806451601</v>
+      </c>
+      <c r="E25">
+        <v>0.58486707566462137</v>
+      </c>
+      <c r="F25">
+        <v>-0.2329428259945775</v>
+      </c>
+      <c r="G25">
+        <v>6</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>2.8389734272087214E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>0.5</v>
+      </c>
+      <c r="B26">
+        <v>1.20047393364928</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>47.4838709677419</v>
+      </c>
+      <c r="E26">
+        <v>0.90417690417690288</v>
+      </c>
+      <c r="F26">
+        <v>-4.3746590551702998E-2</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>2.8389734272087214E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>0.5</v>
+      </c>
+      <c r="B27">
+        <v>1.4003159557661899</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>62.193548387096698</v>
+      </c>
+      <c r="E27">
+        <v>1.6450511945392441</v>
+      </c>
+      <c r="F27">
+        <v>0.21617941788473871</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>2.8389734272087214E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>0.5</v>
+      </c>
+      <c r="B28">
+        <v>1.6001579778830901</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>73.0322580645161</v>
+      </c>
+      <c r="E28">
+        <v>2.7081339712918622</v>
+      </c>
+      <c r="F28">
+        <v>0.43267014507721679</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="0"/>
+        <v>2.8389734272087214E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B29" s="7">
+        <v>0.73475513428119998</v>
+      </c>
+      <c r="C29" s="7">
+        <v>5</v>
+      </c>
+      <c r="D29" s="7">
+        <v>33.5483870967741</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.50485436893203661</v>
+      </c>
+      <c r="F29" s="7">
+        <v>-0.29683388107037489</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>1.4194867136043607E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B30" s="7">
+        <v>0.90157977883096296</v>
+      </c>
+      <c r="C30" s="7">
+        <v>5</v>
+      </c>
+      <c r="D30" s="7">
+        <v>45.935483870967701</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.84964200477326834</v>
+      </c>
+      <c r="F30" s="7">
+        <v>-7.0764024993420827E-2</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>1.4194867136043607E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B31" s="7">
+        <v>1.1170616113744001</v>
+      </c>
+      <c r="C31" s="7">
+        <v>5</v>
+      </c>
+      <c r="D31" s="7">
+        <v>55.741935483870897</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.259475218658888</v>
+      </c>
+      <c r="F31" s="7">
+        <v>0.1001896267721403</v>
+      </c>
+      <c r="G31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="0"/>
+        <v>1.4194867136043607E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B32" s="7">
+        <v>1.38988941548183</v>
+      </c>
+      <c r="C32" s="7">
+        <v>5</v>
+      </c>
+      <c r="D32" s="7">
+        <v>72.516129032257993</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.6384976525821502</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0.42135671213032178</v>
+      </c>
+      <c r="G32">
+        <v>8</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="0"/>
+        <v>1.4194867136043607E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B33" s="7">
+        <v>1.57930489731437</v>
+      </c>
+      <c r="C33" s="7">
+        <v>5</v>
+      </c>
+      <c r="D33" s="7">
+        <v>83.354838709677395</v>
+      </c>
+      <c r="E33" s="7">
+        <v>5.0077519379844873</v>
+      </c>
+      <c r="F33" s="7">
+        <v>0.69964280769583431</v>
+      </c>
+      <c r="G33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="0"/>
+        <v>1.4194867136043607E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>0</v>
+      </c>
+      <c r="B34" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>8.43</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.27618215572785848</v>
+      </c>
+      <c r="F34" s="7">
+        <v>-0.55880438484237782</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>0</v>
+      </c>
+      <c r="B35" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2</v>
+      </c>
+      <c r="D35" s="7">
+        <v>15.59</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.55408126999170715</v>
+      </c>
+      <c r="F35" s="7">
+        <v>-0.25642653036117807</v>
+      </c>
+      <c r="G35">
+        <v>8</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>0</v>
+      </c>
+      <c r="B36" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C36" s="7">
+        <v>3</v>
+      </c>
+      <c r="D36" s="7">
+        <v>20.18</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.75845652718616896</v>
+      </c>
+      <c r="F36" s="7">
+        <v>-0.12006930682745021</v>
+      </c>
+      <c r="G36">
+        <v>8</v>
+      </c>
+      <c r="H36" s="7">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>0</v>
+      </c>
+      <c r="B37" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C37" s="7">
+        <v>4</v>
+      </c>
+      <c r="D37" s="7">
+        <v>28.24</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.1806020066889631</v>
+      </c>
+      <c r="F37" s="7">
+        <v>7.2103517063392866E-2</v>
+      </c>
+      <c r="G37">
+        <v>8</v>
+      </c>
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>0</v>
+      </c>
+      <c r="B38" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C38" s="7">
+        <v>5</v>
+      </c>
+      <c r="D38" s="7">
+        <v>38.65</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.889975550122249</v>
+      </c>
+      <c r="F38" s="7">
+        <v>0.27645618591098309</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H43" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T16"/>
